--- a/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\Downloads\Java-apiCourse-feature\Java-apiCourse-feature\docs\設計\部品在庫管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usaposu\git\Java-apiCourse-staffservice\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BBF29D-7D36-434C-969A-5D86F9ED2D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671BDED7-74B2-496C-AE48-06D256D27A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
     <sheet name="機能概要" sheetId="1" r:id="rId2"/>
     <sheet name="リクエスト" sheetId="23" r:id="rId3"/>
     <sheet name="レスポンス" sheetId="24" r:id="rId4"/>
+    <sheet name="シーケンス" sheetId="25" r:id="rId5"/>
+    <sheet name="処理詳細" sheetId="26" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$Y$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$27</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="285">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -216,9 +218,6 @@
     <t>取引種別</t>
   </si>
   <si>
-    <t>transaction_type</t>
-  </si>
-  <si>
     <t>String</t>
   </si>
   <si>
@@ -231,63 +230,30 @@
     <t>入荷日時</t>
   </si>
   <si>
-    <t>transaction_date</t>
-  </si>
-  <si>
-    <t>業務上の処理日時（入荷日時）</t>
-  </si>
-  <si>
-    <t>ISO 8601</t>
-  </si>
-  <si>
     <t>"2024-12-15T14:30:00Z"</t>
   </si>
   <si>
     <t xml:space="preserve">仕入先名 </t>
   </si>
   <si>
-    <t>supplier_name</t>
-  </si>
-  <si>
-    <t>仕入先企業名</t>
-  </si>
-  <si>
     <t>"株式会社サプライヤーA"</t>
   </si>
   <si>
     <t>発注書番号</t>
   </si>
   <si>
-    <t>purchase_order_no</t>
-  </si>
-  <si>
     <t>"PO-2024-001234"</t>
   </si>
   <si>
     <t>入荷作業者名</t>
   </si>
   <si>
-    <t>operator_name</t>
-  </si>
-  <si>
-    <t>処理担当者名</t>
-  </si>
-  <si>
     <t>"購買太郎"</t>
   </si>
   <si>
-    <t>入荷部品リスト</t>
-  </si>
-  <si>
-    <t>items</t>
-  </si>
-  <si>
     <t>Array</t>
   </si>
   <si>
-    <t>下記 ”入荷部品リスト（items）配列仕様” 参照</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -297,49 +263,22 @@
     <t>在庫ID</t>
   </si>
   <si>
-    <t>stock_id</t>
-  </si>
-  <si>
     <t>製品在庫のID</t>
   </si>
   <si>
-    <t>入荷先センター ID</t>
-  </si>
-  <si>
-    <t>center_id</t>
-  </si>
-  <si>
     <t>Integer</t>
   </si>
   <si>
     <t>カテゴリID</t>
   </si>
   <si>
-    <t>カテゴリ ID</t>
-  </si>
-  <si>
-    <t>category_id</t>
-  </si>
-  <si>
     <t>部品名</t>
   </si>
   <si>
-    <t>parts_name</t>
-  </si>
-  <si>
     <t>“ボールベアリング”</t>
   </si>
   <si>
     <t>入荷数量</t>
-  </si>
-  <si>
-    <t>receive_amount</t>
-  </si>
-  <si>
-    <t>部品説明</t>
-  </si>
-  <si>
-    <t>description</t>
   </si>
   <si>
     <t>部品在庫に関する説明</t>
@@ -434,12 +373,1095 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>処理詳細</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>処理</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t>/api/parts/stock/receive</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>宇佐美</t>
+    <rPh sb="0" eb="3">
+      <t>ウサミ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫管理システム</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品在入荷 API</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>処理フロー</t>
+  </si>
+  <si>
+    <t>シーケンス</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>宇佐美</t>
+    <rPh sb="0" eb="3">
+      <t>ウサミ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>amoibe</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>×× ××</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>データフォーマット</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>URL: POST /api/parts/stock/receive</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Authorization: Bearer &lt;JWT_TOKEN&gt;</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>取引種別</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>取引種別</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>取引種別（必須）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷日時</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷日時（必須）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">仕入先名 </t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>仕入先名（必須）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>発注書番号</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>発注書番号（必須）</t>
+    <rPh sb="6" eb="8">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷作業者名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷作業者名（必須）</t>
+    <rPh sb="7" eb="9">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷部品リスト</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷部品リスト（必須）</t>
+    <rPh sb="8" eb="10">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷部品リスト配列仕様：</t>
+    <rPh sb="7" eb="9">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ヘッダー：</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>パラメータ：</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>在庫ID（必須）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷先センター ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷先センター ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カテゴリ ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カテゴリ ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷数量</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷数量</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品説明</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品説明</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷先センター ID（必須）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カテゴリ ID（必須）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品名（必須）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷数量（必須）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1．パラメータ設定</t>
+    <rPh sb="7" eb="9">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>PartsReceivingUpdateDTO</t>
+  </si>
+  <si>
+    <t>PartsReceivingUpdateDTO</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>リクエストパラメータを、部品入荷更新DTO(PartsReceivingUpdateDTO)に設定する。</t>
+    <rPh sb="12" eb="14">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>設定元：リクエストパラメータ</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品入荷更新DTO</t>
+    <rPh sb="2" eb="4">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_type</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>transaction_type</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_date</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>transaction_date</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>supplier_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>supplier_name</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>purchase_order_no</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>purchase_order_no</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>operator_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>operator_name</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>items</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>items</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>業務上の処理日時（入荷日時）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>仕入先企業名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>仕入先企業名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>発注書番号</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>処理担当者名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>処理担当者名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>下記 ”入荷部品リスト（items）配列仕様” 参照</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷日時</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷部品リスト</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>items配列</t>
+    <rPh sb="5" eb="7">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>stock_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>stock_id</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>center_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>center_id</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>category_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>category_id</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>parts_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>parts_name</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>receive_amount</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>receive_amount</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2．入力チェック</t>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>処理中にエラーが発生した場合は、エラーレスポンスを返却し処理を終了する。</t>
+  </si>
+  <si>
+    <t>バリデータ（PartsReceivingUpdateValidator）を使用し、PartsReceivingUpdateDTOの入力チェックを行う。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>チェック対象</t>
+  </si>
+  <si>
+    <t>対象項目名</t>
+  </si>
+  <si>
+    <t>チェック条件</t>
+  </si>
+  <si>
+    <t>入力パラメータ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_typeは必須項目です。</t>
+    <rPh sb="17" eb="19">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_dateは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>supplier_nameは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>purchase_order_noは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>operator_nameは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_type=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>transaction_date=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>supplier_name=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>purchase_order_no=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>operator_name=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>stock_id=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>center_id=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>category_id=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>parts_name=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>receive_amount=NULL</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>stock_idは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>center_idは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>category_idは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>parts_nameは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>receive_amountは必須項目です。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>センターID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>その他エラー</t>
+  </si>
+  <si>
+    <t>不明なエラー</t>
+  </si>
+  <si>
+    <t>3．部品入荷更新</t>
+    <rPh sb="2" eb="4">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>サービス（PartsReceivingUpdateService.java）を呼び出し、検索条件に一致する在庫テーブルが存在すれば数量を更新、存在しなければ新規行を登録をする。</t>
+    <rPh sb="39" eb="40">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>項目名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>在庫ID</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チェック条件</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>&lt;結合条件＞</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品入出庫履歴テーブルの在庫ID＝部品在庫テーブルの在庫ID</t>
+    <rPh sb="0" eb="2">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ニュウシュッコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ザイコ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>＜部品入出庫履歴更新＞</t>
+    <rPh sb="1" eb="3">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ニュウシュッコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>検索在庫IDが在庫テーブルに存在するかどうか</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>更新内容</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>更新条件</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>検索在庫IDが在庫テーブルに存在する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>検索在庫IDが在庫テーブルに存在しない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫IDを新規行で登録</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>更新項目</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>リクエストの transaction_type が "RECEIVE" であること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ISO 8601</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>リクエストのtransaction_dateがISO 8601であること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>リクエストのoperator_nameをそのまま使用</t>
+    <rPh sb="24" eb="26">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>リクエストのpurchase_order_noをそのまま使用</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>リクエストのsupplier_nameをそのまま使用</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫テーブル更新対象のstock_id</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫テーブル更新対象のreceive_amount</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>＜部品在庫テーブル更新＞</t>
+    <rPh sb="1" eb="3">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>＜部品在庫テーブルのID有無チェック＞</t>
+    <rPh sb="1" eb="3">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ウム</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>センターIDを新規行で登録</t>
+    <rPh sb="7" eb="9">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カテゴリIDを新規行で登録</t>
+    <rPh sb="7" eb="9">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品名を新規行で登録</t>
+    <rPh sb="0" eb="3">
+      <t>ブヒンメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入荷数量を新規行で登録</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象在庫IDの数量に入荷数量を加算</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品説明を新規行で登録</t>
+    <rPh sb="0" eb="2">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>検索在庫IDが在庫テーブルに存在しない
+部品説明が指定リストに含まれる場合</t>
+    <rPh sb="20" eb="22">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>AND　部品入出庫履歴テーブルの入荷後数量＝部品在庫テーブルの入荷後数量</t>
+    <rPh sb="16" eb="18">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ニュウカ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>スウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>4．レスポンス構築</t>
+    <rPh sb="7" eb="9">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>(1)3．の処理でマッピングしたDTOをAPIの共通レスポンス（ApiResponse）に設定し、返却する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>APIの共通レスポンス</t>
+  </si>
+  <si>
+    <t>処理結果メッセージ</t>
+  </si>
+  <si>
+    <t>(2)認証トークンが無効または未付与の場合、エラーメッセージを返却する</t>
+    <rPh sb="3" eb="5">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ムコウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"401"</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"error"</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>(3)2．の処理で入力値の不備やシステム例外が発生した場合、以下の形式でレスポンスを返却する</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>error_code</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>details</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>timestamp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>エラーコード</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>エラー詳細</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>日時</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>1.1</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>宇佐美</t>
+    <rPh sb="0" eb="3">
+      <t>ウサミ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>シーケンスシート作成</t>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>処理詳細シート作成</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ApiResponse</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -508,6 +1530,84 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -535,7 +1635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -688,16 +1788,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,12 +1949,144 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -869,158 +2117,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1031,40 +2132,64 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1073,29 +2198,231 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
@@ -1732,6 +3059,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1263068</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4DCD75B-1B57-B134-A979-B7D994D1B8FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="761999" y="2250284"/>
+          <a:ext cx="8121069" cy="7227092"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -1991,7 +3373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="38"/>
     <col min="2" max="2" width="5.109375" style="39" customWidth="1"/>
@@ -2001,12 +3383,12 @@
     <col min="6" max="16384" width="3.6640625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.8">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B2" s="40" t="s">
         <v>1</v>
       </c>
@@ -2020,7 +3402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B3" s="42" t="s">
         <v>5</v>
       </c>
@@ -2034,403 +3416,420 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="42"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="45"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B4" s="199" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="43">
+        <v>45983</v>
+      </c>
+      <c r="D4" s="193" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="177" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B5" s="200"/>
+      <c r="C5" s="43">
+        <v>45983</v>
+      </c>
+      <c r="D5" s="193" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="177" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E6" s="193"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B7" s="42"/>
       <c r="C7" s="44"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B8" s="42"/>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
       <c r="E8" s="44"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B9" s="42"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B10" s="42"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B11" s="42"/>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
       <c r="E11" s="44"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B12" s="42"/>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
       <c r="E12" s="44"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B13" s="42"/>
       <c r="C13" s="44"/>
       <c r="D13" s="44"/>
       <c r="E13" s="44"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B14" s="42"/>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
       <c r="E14" s="44"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B15" s="42"/>
       <c r="C15" s="44"/>
       <c r="D15" s="44"/>
       <c r="E15" s="44"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B16" s="42"/>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B17" s="42"/>
       <c r="C17" s="44"/>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B18" s="42"/>
       <c r="C18" s="44"/>
       <c r="D18" s="44"/>
       <c r="E18" s="44"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B19" s="42"/>
       <c r="C19" s="44"/>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B20" s="42"/>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B21" s="42"/>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
       <c r="E21" s="44"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B22" s="42"/>
       <c r="C22" s="44"/>
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B23" s="42"/>
       <c r="C23" s="44"/>
       <c r="D23" s="44"/>
       <c r="E23" s="44"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B24" s="42"/>
       <c r="C24" s="44"/>
       <c r="D24" s="44"/>
       <c r="E24" s="44"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B25" s="42"/>
       <c r="C25" s="44"/>
       <c r="D25" s="44"/>
       <c r="E25" s="44"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B26" s="42"/>
       <c r="C26" s="44"/>
       <c r="D26" s="44"/>
       <c r="E26" s="44"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B27" s="42"/>
       <c r="C27" s="44"/>
       <c r="D27" s="44"/>
       <c r="E27" s="44"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B28" s="42"/>
       <c r="C28" s="44"/>
       <c r="D28" s="44"/>
       <c r="E28" s="44"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B29" s="42"/>
       <c r="C29" s="44"/>
       <c r="D29" s="44"/>
       <c r="E29" s="44"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B30" s="42"/>
       <c r="C30" s="44"/>
       <c r="D30" s="44"/>
       <c r="E30" s="44"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B31" s="42"/>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B32" s="42"/>
       <c r="C32" s="44"/>
       <c r="D32" s="44"/>
       <c r="E32" s="44"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B33" s="42"/>
       <c r="C33" s="44"/>
       <c r="D33" s="44"/>
       <c r="E33" s="44"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B34" s="42"/>
       <c r="C34" s="44"/>
       <c r="D34" s="44"/>
       <c r="E34" s="44"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B35" s="42"/>
       <c r="C35" s="44"/>
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B36" s="42"/>
       <c r="C36" s="44"/>
       <c r="D36" s="44"/>
       <c r="E36" s="44"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B37" s="42"/>
       <c r="C37" s="44"/>
       <c r="D37" s="44"/>
       <c r="E37" s="44"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B38" s="42"/>
       <c r="C38" s="44"/>
       <c r="D38" s="44"/>
       <c r="E38" s="44"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B39" s="42"/>
       <c r="C39" s="44"/>
       <c r="D39" s="44"/>
       <c r="E39" s="44"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B40" s="42"/>
       <c r="C40" s="44"/>
       <c r="D40" s="44"/>
       <c r="E40" s="44"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B41" s="42"/>
       <c r="C41" s="44"/>
       <c r="D41" s="44"/>
       <c r="E41" s="44"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B42" s="42"/>
       <c r="C42" s="44"/>
       <c r="D42" s="44"/>
       <c r="E42" s="44"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B43" s="42"/>
       <c r="C43" s="44"/>
       <c r="D43" s="44"/>
       <c r="E43" s="44"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B44" s="42"/>
       <c r="C44" s="44"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B45" s="42"/>
       <c r="C45" s="44"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B46" s="42"/>
       <c r="C46" s="44"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B47" s="42"/>
       <c r="C47" s="44"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B48" s="42"/>
       <c r="C48" s="44"/>
       <c r="D48" s="44"/>
       <c r="E48" s="44"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B49" s="42"/>
       <c r="C49" s="44"/>
       <c r="D49" s="44"/>
       <c r="E49" s="44"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B50" s="42"/>
       <c r="C50" s="44"/>
       <c r="D50" s="44"/>
       <c r="E50" s="44"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B51" s="42"/>
       <c r="C51" s="44"/>
       <c r="D51" s="44"/>
       <c r="E51" s="44"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B52" s="42"/>
       <c r="C52" s="44"/>
       <c r="D52" s="44"/>
       <c r="E52" s="44"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B53" s="42"/>
       <c r="C53" s="44"/>
       <c r="D53" s="44"/>
       <c r="E53" s="44"/>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B54" s="42"/>
       <c r="C54" s="44"/>
       <c r="D54" s="44"/>
       <c r="E54" s="44"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B55" s="42"/>
       <c r="C55" s="44"/>
       <c r="D55" s="44"/>
       <c r="E55" s="44"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B56" s="42"/>
       <c r="C56" s="44"/>
       <c r="D56" s="44"/>
       <c r="E56" s="44"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B57" s="42"/>
       <c r="C57" s="44"/>
       <c r="D57" s="44"/>
       <c r="E57" s="44"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B58" s="42"/>
       <c r="C58" s="44"/>
       <c r="D58" s="44"/>
       <c r="E58" s="44"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B59" s="42"/>
       <c r="C59" s="44"/>
       <c r="D59" s="44"/>
       <c r="E59" s="44"/>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B60" s="42"/>
       <c r="C60" s="44"/>
       <c r="D60" s="44"/>
       <c r="E60" s="44"/>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B61" s="42"/>
       <c r="C61" s="44"/>
       <c r="D61" s="44"/>
       <c r="E61" s="44"/>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B62" s="42"/>
       <c r="C62" s="44"/>
       <c r="D62" s="44"/>
       <c r="E62" s="44"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B63" s="42"/>
       <c r="C63" s="44"/>
       <c r="D63" s="44"/>
       <c r="E63" s="44"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B64" s="42"/>
       <c r="C64" s="44"/>
       <c r="D64" s="44"/>
       <c r="E64" s="44"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B65" s="42"/>
       <c r="C65" s="44"/>
       <c r="D65" s="44"/>
       <c r="E65" s="44"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B66" s="42"/>
       <c r="C66" s="44"/>
       <c r="D66" s="44"/>
       <c r="E66" s="44"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B67" s="42"/>
       <c r="C67" s="44"/>
       <c r="D67" s="44"/>
       <c r="E67" s="44"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B68" s="42"/>
       <c r="C68" s="44"/>
       <c r="D68" s="44"/>
       <c r="E68" s="44"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B69" s="42"/>
       <c r="C69" s="44"/>
       <c r="D69" s="44"/>
       <c r="E69" s="44"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:B5"/>
+  </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2439,7 +3838,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH26"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="20" width="3.6640625" style="29"/>
     <col min="21" max="21" width="5.88671875" style="29" customWidth="1"/>
@@ -2448,488 +3847,488 @@
     <col min="35" max="16384" width="3.6640625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="86" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="92" t="s">
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="66" t="s">
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="96" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="71" t="s">
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z1" s="77"/>
+      <c r="AA1" s="77"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="67" t="s">
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-    </row>
-    <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="66"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="100"/>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-    </row>
-    <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="86" t="s">
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+    </row>
+    <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+    </row>
+    <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="92" t="s">
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="93"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="66" t="s">
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="66"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="66" t="s">
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="78"/>
+      <c r="AC3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-    </row>
-    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="70"/>
-      <c r="AH4" s="70"/>
-    </row>
-    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="47" t="s">
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="46"/>
+      <c r="AF3" s="53">
+        <v>45983</v>
+      </c>
+      <c r="AG3" s="54"/>
+      <c r="AH3" s="54"/>
+    </row>
+    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="56"/>
+    </row>
+    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="50" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="51"/>
-      <c r="AE5" s="51"/>
-      <c r="AF5" s="51"/>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
-    </row>
-    <row r="6" spans="1:34" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="47" t="s">
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="95"/>
+      <c r="U5" s="95"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+      <c r="X5" s="95"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95"/>
+      <c r="AB5" s="95"/>
+      <c r="AC5" s="95"/>
+      <c r="AD5" s="95"/>
+      <c r="AE5" s="95"/>
+      <c r="AF5" s="95"/>
+      <c r="AG5" s="95"/>
+      <c r="AH5" s="95"/>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="131" t="s">
-        <v>132</v>
-      </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="51"/>
-      <c r="AH6" s="51"/>
-    </row>
-    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="47" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="101" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="95"/>
+      <c r="T6" s="95"/>
+      <c r="U6" s="95"/>
+      <c r="V6" s="95"/>
+      <c r="W6" s="95"/>
+      <c r="X6" s="95"/>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="95"/>
+      <c r="AA6" s="95"/>
+      <c r="AB6" s="95"/>
+      <c r="AC6" s="95"/>
+      <c r="AD6" s="95"/>
+      <c r="AE6" s="95"/>
+      <c r="AF6" s="95"/>
+      <c r="AG6" s="95"/>
+      <c r="AH6" s="95"/>
+    </row>
+    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="51"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-    </row>
-    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="47" t="s">
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="95"/>
+      <c r="W7" s="95"/>
+      <c r="X7" s="95"/>
+      <c r="Y7" s="95"/>
+      <c r="Z7" s="95"/>
+      <c r="AA7" s="95"/>
+      <c r="AB7" s="95"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="95"/>
+      <c r="AE7" s="95"/>
+      <c r="AF7" s="95"/>
+      <c r="AG7" s="95"/>
+      <c r="AH7" s="95"/>
+    </row>
+    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A8" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
-    </row>
-    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="47" t="s">
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="95"/>
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+      <c r="T8" s="95"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="95"/>
+      <c r="W8" s="95"/>
+      <c r="X8" s="95"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="95"/>
+      <c r="AE8" s="95"/>
+      <c r="AF8" s="95"/>
+      <c r="AG8" s="95"/>
+      <c r="AH8" s="95"/>
+    </row>
+    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="50" t="s">
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-    </row>
-    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="52" t="s">
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="95"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+      <c r="S9" s="95"/>
+      <c r="T9" s="95"/>
+      <c r="U9" s="95"/>
+      <c r="V9" s="95"/>
+      <c r="W9" s="95"/>
+      <c r="X9" s="95"/>
+      <c r="Y9" s="95"/>
+      <c r="Z9" s="95"/>
+      <c r="AA9" s="95"/>
+      <c r="AB9" s="95"/>
+      <c r="AC9" s="95"/>
+      <c r="AD9" s="95"/>
+      <c r="AE9" s="95"/>
+      <c r="AF9" s="95"/>
+      <c r="AG9" s="95"/>
+      <c r="AH9" s="95"/>
+    </row>
+    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A10" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55" t="s">
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="56"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="56"/>
-      <c r="AH10" s="56"/>
-    </row>
-    <row r="11" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="57" t="s">
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="100"/>
+      <c r="S10" s="100"/>
+      <c r="T10" s="100"/>
+      <c r="U10" s="100"/>
+      <c r="V10" s="100"/>
+      <c r="W10" s="100"/>
+      <c r="X10" s="100"/>
+      <c r="Y10" s="100"/>
+      <c r="Z10" s="100"/>
+      <c r="AA10" s="100"/>
+      <c r="AB10" s="100"/>
+      <c r="AC10" s="100"/>
+      <c r="AD10" s="100"/>
+      <c r="AE10" s="100"/>
+      <c r="AF10" s="100"/>
+      <c r="AG10" s="100"/>
+      <c r="AH10" s="100"/>
+    </row>
+    <row r="11" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A11" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="58"/>
-      <c r="Y11" s="58"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="58"/>
-      <c r="AC11" s="58"/>
-      <c r="AD11" s="58"/>
-      <c r="AE11" s="58"/>
-      <c r="AF11" s="58"/>
-      <c r="AG11" s="58"/>
-      <c r="AH11" s="58"/>
-    </row>
-    <row r="12" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="86"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="86"/>
+      <c r="Z11" s="86"/>
+      <c r="AA11" s="86"/>
+      <c r="AB11" s="86"/>
+      <c r="AC11" s="86"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="86"/>
+      <c r="AF11" s="86"/>
+      <c r="AG11" s="86"/>
+      <c r="AH11" s="86"/>
+    </row>
+    <row r="12" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="30"/>
     </row>
-    <row r="13" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="30"/>
     </row>
-    <row r="14" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="30"/>
     </row>
-    <row r="15" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="30"/>
     </row>
-    <row r="16" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="30"/>
     </row>
-    <row r="17" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="30"/>
     </row>
-    <row r="18" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="30"/>
     </row>
-    <row r="19" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="30"/>
     </row>
-    <row r="20" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="30"/>
     </row>
-    <row r="21" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="30"/>
     </row>
-    <row r="22" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A22" s="30"/>
     </row>
-    <row r="23" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="31"/>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -2965,21 +4364,21 @@
       <c r="AG23" s="32"/>
       <c r="AH23" s="32"/>
     </row>
-    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="59" t="s">
+    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A24" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="59" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="60"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="88"/>
       <c r="K24" s="36" t="s">
         <v>32</v>
       </c>
@@ -2992,34 +4391,34 @@
       <c r="N24" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="O24" s="62" t="s">
+      <c r="O24" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="62"/>
-      <c r="AB24" s="62"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="62"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-    </row>
-    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="63">
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="90"/>
+      <c r="Z24" s="90"/>
+      <c r="AA24" s="90"/>
+      <c r="AB24" s="90"/>
+      <c r="AC24" s="90"/>
+      <c r="AD24" s="90"/>
+      <c r="AE24" s="90"/>
+      <c r="AF24" s="90"/>
+      <c r="AG24" s="90"/>
+      <c r="AH24" s="90"/>
+    </row>
+    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A25" s="82">
         <v>1</v>
       </c>
-      <c r="B25" s="64"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="34" t="s">
         <v>37</v>
       </c>
@@ -3040,33 +4439,33 @@
         <v>38</v>
       </c>
       <c r="N25" s="34"/>
-      <c r="O25" s="65"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="65"/>
-      <c r="AC25" s="65"/>
-      <c r="AD25" s="65"/>
-      <c r="AE25" s="65"/>
-      <c r="AF25" s="65"/>
-      <c r="AG25" s="65"/>
-      <c r="AH25" s="65"/>
-    </row>
-    <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="63">
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="84"/>
+      <c r="T25" s="84"/>
+      <c r="U25" s="84"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="84"/>
+      <c r="X25" s="84"/>
+      <c r="Y25" s="84"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="84"/>
+      <c r="AB25" s="84"/>
+      <c r="AC25" s="84"/>
+      <c r="AD25" s="84"/>
+      <c r="AE25" s="84"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="84"/>
+      <c r="AH25" s="84"/>
+    </row>
+    <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A26" s="82">
         <v>2</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="46" t="s">
+      <c r="B26" s="83"/>
+      <c r="C26" s="45" t="s">
         <v>39</v>
       </c>
       <c r="D26" s="35"/>
@@ -3082,39 +4481,36 @@
       </c>
       <c r="M26" s="37"/>
       <c r="N26" s="34"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
-      <c r="V26" s="65"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="65"/>
-      <c r="AC26" s="65"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="65"/>
-      <c r="AF26" s="65"/>
-      <c r="AG26" s="65"/>
-      <c r="AH26" s="65"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="84"/>
+      <c r="Q26" s="84"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="84"/>
+      <c r="T26" s="84"/>
+      <c r="U26" s="84"/>
+      <c r="V26" s="84"/>
+      <c r="W26" s="84"/>
+      <c r="X26" s="84"/>
+      <c r="Y26" s="84"/>
+      <c r="Z26" s="84"/>
+      <c r="AA26" s="84"/>
+      <c r="AB26" s="84"/>
+      <c r="AC26" s="84"/>
+      <c r="AD26" s="84"/>
+      <c r="AE26" s="84"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="84"/>
+      <c r="AH26" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="AC1:AE2"/>
-    <mergeCell ref="AF1:AH2"/>
-    <mergeCell ref="A1:K4"/>
-    <mergeCell ref="L1:P2"/>
-    <mergeCell ref="Q1:U2"/>
-    <mergeCell ref="L3:P4"/>
-    <mergeCell ref="Q3:U4"/>
-    <mergeCell ref="Y1:AB2"/>
-    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="H10:AH10"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:AH5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:AH6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:AH7"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="O26:AH26"/>
     <mergeCell ref="V3:X4"/>
@@ -3131,13 +4527,16 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="H9:AH9"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H10:AH10"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:AH5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:AH6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:AH7"/>
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="AC1:AE2"/>
+    <mergeCell ref="AF1:AH2"/>
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="L1:P2"/>
+    <mergeCell ref="Q1:U2"/>
+    <mergeCell ref="L3:P4"/>
+    <mergeCell ref="Q3:U4"/>
+    <mergeCell ref="Y1:AB2"/>
+    <mergeCell ref="Y3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3149,7 +4548,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y27"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="6" style="4" customWidth="1"/>
     <col min="2" max="4" width="3.6640625" style="4"/>
@@ -3168,568 +4567,568 @@
     <col min="26" max="16384" width="3.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="86" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="92" t="s">
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="66" t="s">
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="96" t="s">
+      <c r="U1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="97"/>
-      <c r="W1" s="71" t="s">
+      <c r="V1" s="77"/>
+      <c r="W1" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="67" t="s">
+      <c r="X1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="68"/>
-    </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="70"/>
-    </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="86" t="s">
+      <c r="Y1" s="54"/>
+    </row>
+    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="56"/>
+    </row>
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="92" t="s">
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="66" t="s">
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="V3" s="97"/>
-      <c r="W3" s="66" t="s">
+      <c r="U3" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="V3" s="77"/>
+      <c r="W3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="67" t="s">
+      <c r="X3" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="68"/>
-    </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="70"/>
-    </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="102" t="s">
+      <c r="Y3" s="54"/>
+    </row>
+    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="56"/>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="102" t="s">
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="103" t="s">
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
       <c r="T5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="U5" s="103" t="s">
+      <c r="U5" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-    </row>
-    <row r="6" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V5" s="120"/>
+      <c r="W5" s="120"/>
+      <c r="X5" s="120"/>
+      <c r="Y5" s="120"/>
+    </row>
+    <row r="6" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A6" s="24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
       <c r="J7" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="104" t="s">
+      <c r="K7" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="66" t="s">
+      <c r="L7" s="116"/>
+      <c r="M7" s="116"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66" t="s">
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="T7" s="66"/>
-      <c r="U7" s="104" t="s">
+      <c r="T7" s="46"/>
+      <c r="U7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="V7" s="105"/>
-      <c r="W7" s="105"/>
-      <c r="X7" s="105"/>
-      <c r="Y7" s="105"/>
-    </row>
-    <row r="8" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V7" s="116"/>
+      <c r="W7" s="116"/>
+      <c r="X7" s="116"/>
+      <c r="Y7" s="116"/>
+    </row>
+    <row r="8" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="11">
         <v>1</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
       <c r="J8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="108" t="s">
+      <c r="K8" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="111">
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="105"/>
+      <c r="O8" s="102">
         <v>4000</v>
       </c>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="111"/>
-      <c r="S8" s="111" t="s">
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102"/>
+      <c r="R8" s="102"/>
+      <c r="S8" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="T8" s="111"/>
-      <c r="U8" s="108" t="s">
+      <c r="T8" s="102"/>
+      <c r="U8" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="109"/>
-    </row>
-    <row r="9" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V8" s="104"/>
+      <c r="W8" s="104"/>
+      <c r="X8" s="104"/>
+      <c r="Y8" s="104"/>
+    </row>
+    <row r="9" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="24"/>
     </row>
-    <row r="10" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66" t="s">
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66" t="s">
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66" t="s">
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="112" t="s">
+      <c r="P11" s="46"/>
+      <c r="Q11" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="112"/>
-      <c r="S11" s="112"/>
-      <c r="T11" s="112"/>
-      <c r="U11" s="66" t="s">
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="104" t="s">
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="Y11" s="105"/>
-    </row>
-    <row r="12" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y11" s="116"/>
+    </row>
+    <row r="12" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111" t="s">
+      <c r="B12" s="162" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="162" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="108" t="s">
+      <c r="L12" s="104"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="P12" s="107"/>
+      <c r="Q12" s="162" t="s">
+        <v>129</v>
+      </c>
+      <c r="R12" s="102"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="102"/>
+      <c r="U12" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111"/>
-      <c r="T12" s="111"/>
-      <c r="U12" s="115" t="s">
+      <c r="V12" s="102"/>
+      <c r="W12" s="102"/>
+      <c r="X12" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="V12" s="111"/>
-      <c r="W12" s="111"/>
-      <c r="X12" s="111" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y12" s="111"/>
-    </row>
-    <row r="13" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y12" s="102"/>
+    </row>
+    <row r="13" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A13" s="11">
         <v>2</v>
       </c>
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="162" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="170" t="s">
+        <v>169</v>
+      </c>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="108"/>
+      <c r="K13" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="163" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="195" t="s">
+        <v>248</v>
+      </c>
+      <c r="V13" s="102"/>
+      <c r="W13" s="102"/>
+      <c r="X13" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="116" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="116"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
-      <c r="X13" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y13" s="111"/>
-    </row>
-    <row r="14" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y13" s="102"/>
+    </row>
+    <row r="14" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A14" s="11">
         <v>3</v>
       </c>
-      <c r="B14" s="117" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="113" t="s">
+      <c r="B14" s="163" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="162" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="111" t="s">
-        <v>73</v>
-      </c>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="115"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
-      <c r="X14" s="118" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y14" s="119"/>
-    </row>
-    <row r="15" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="P14" s="107"/>
+      <c r="Q14" s="162" t="s">
+        <v>180</v>
+      </c>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="117"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="102"/>
+      <c r="X14" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y14" s="110"/>
+    </row>
+    <row r="15" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A15" s="11">
         <v>4</v>
       </c>
-      <c r="B15" s="111" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="113" t="s">
+      <c r="B15" s="162" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="162" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="104"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="111" t="s">
-        <v>75</v>
-      </c>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
-      <c r="X15" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y15" s="110"/>
-    </row>
-    <row r="16" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="P15" s="107"/>
+      <c r="Q15" s="162" t="s">
+        <v>136</v>
+      </c>
+      <c r="R15" s="102"/>
+      <c r="S15" s="102"/>
+      <c r="T15" s="102"/>
+      <c r="U15" s="102"/>
+      <c r="V15" s="102"/>
+      <c r="W15" s="102"/>
+      <c r="X15" s="103" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y15" s="105"/>
+    </row>
+    <row r="16" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A16" s="11">
         <v>5</v>
       </c>
-      <c r="B16" s="111" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="113" t="s">
+      <c r="B16" s="162" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="162" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="105"/>
+      <c r="O16" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="108" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y16" s="110"/>
-    </row>
-    <row r="17" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="P16" s="107"/>
+      <c r="Q16" s="162" t="s">
+        <v>183</v>
+      </c>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="102"/>
+      <c r="U16" s="102"/>
+      <c r="V16" s="102"/>
+      <c r="W16" s="102"/>
+      <c r="X16" s="103" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y16" s="105"/>
+    </row>
+    <row r="17" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A17" s="11">
         <v>6</v>
       </c>
-      <c r="B17" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="108" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="113" t="s">
+      <c r="B17" s="162" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="162" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" s="104"/>
+      <c r="M17" s="104"/>
+      <c r="N17" s="105"/>
+      <c r="O17" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="120" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" s="109"/>
-      <c r="S17" s="109"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="109"/>
-      <c r="V17" s="109"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="108" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y17" s="110"/>
-    </row>
-    <row r="18" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="P17" s="107"/>
+      <c r="Q17" s="171" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="104"/>
+      <c r="S17" s="104"/>
+      <c r="T17" s="104"/>
+      <c r="U17" s="104"/>
+      <c r="V17" s="104"/>
+      <c r="W17" s="105"/>
+      <c r="X17" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y17" s="105"/>
+    </row>
+    <row r="18" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A18" s="26"/>
       <c r="B18" s="27"/>
       <c r="C18" s="27"/>
@@ -3756,9 +5155,9 @@
       <c r="X18" s="27"/>
       <c r="Y18" s="27"/>
     </row>
-    <row r="19" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A19" s="26" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
@@ -3785,310 +5184,411 @@
       <c r="X19" s="27"/>
       <c r="Y19" s="27"/>
     </row>
-    <row r="20" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66" t="s">
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66" t="s">
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="112" t="s">
+      <c r="P20" s="46"/>
+      <c r="Q20" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="R20" s="112"/>
-      <c r="S20" s="112"/>
-      <c r="T20" s="112"/>
-      <c r="U20" s="66" t="s">
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="V20" s="66"/>
-      <c r="W20" s="66"/>
-      <c r="X20" s="104" t="s">
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="Y20" s="105"/>
-    </row>
-    <row r="21" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y20" s="116"/>
+    </row>
+    <row r="21" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A21" s="11">
         <v>1</v>
       </c>
-      <c r="B21" s="111" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="113" t="s">
+      <c r="B21" s="162" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="170" t="s">
+        <v>189</v>
+      </c>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="104"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="105"/>
+      <c r="O21" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="111" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111"/>
-      <c r="U21" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V21" s="111"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="121">
+      <c r="P21" s="107"/>
+      <c r="Q21" s="102" t="s">
+        <v>77</v>
+      </c>
+      <c r="R21" s="102"/>
+      <c r="S21" s="102"/>
+      <c r="T21" s="102"/>
+      <c r="U21" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V21" s="102"/>
+      <c r="W21" s="102"/>
+      <c r="X21" s="112">
         <v>5</v>
       </c>
-      <c r="Y21" s="122"/>
-    </row>
-    <row r="22" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y21" s="113"/>
+    </row>
+    <row r="22" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A22" s="11">
         <v>2</v>
       </c>
-      <c r="B22" s="111" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="113" t="s">
+      <c r="B22" s="162" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="162" t="s">
+        <v>191</v>
+      </c>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="L22" s="104"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="111"/>
-      <c r="U22" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V22" s="111"/>
-      <c r="W22" s="111"/>
-      <c r="X22" s="111">
+      <c r="P22" s="107"/>
+      <c r="Q22" s="163" t="s">
+        <v>229</v>
+      </c>
+      <c r="R22" s="102"/>
+      <c r="S22" s="102"/>
+      <c r="T22" s="102"/>
+      <c r="U22" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V22" s="102"/>
+      <c r="W22" s="102"/>
+      <c r="X22" s="102">
         <v>2</v>
       </c>
-      <c r="Y22" s="111"/>
-    </row>
-    <row r="23" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y22" s="102"/>
+    </row>
+    <row r="23" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A23" s="11">
         <v>3</v>
       </c>
-      <c r="B23" s="111" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L23" s="109"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="113" t="s">
+      <c r="B23" s="162" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="162" t="s">
+        <v>193</v>
+      </c>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
-      <c r="X23" s="121">
+      <c r="P23" s="107"/>
+      <c r="Q23" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="R23" s="102"/>
+      <c r="S23" s="102"/>
+      <c r="T23" s="102"/>
+      <c r="U23" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V23" s="102"/>
+      <c r="W23" s="102"/>
+      <c r="X23" s="112">
         <v>1</v>
       </c>
-      <c r="Y23" s="122"/>
-    </row>
-    <row r="24" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y23" s="113"/>
+    </row>
+    <row r="24" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A24" s="11">
         <v>4</v>
       </c>
-      <c r="B24" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="116" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L24" s="109"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="113" t="s">
+      <c r="B24" s="162" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="102"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="170" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y24" s="111"/>
-    </row>
-    <row r="25" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="P24" s="107"/>
+      <c r="Q24" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="R24" s="102"/>
+      <c r="S24" s="102"/>
+      <c r="T24" s="102"/>
+      <c r="U24" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V24" s="102"/>
+      <c r="W24" s="102"/>
+      <c r="X24" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y24" s="102"/>
+    </row>
+    <row r="25" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A25" s="11">
         <v>5</v>
       </c>
-      <c r="B25" s="111" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="113" t="s">
+      <c r="B25" s="162" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="162" t="s">
+        <v>197</v>
+      </c>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
-      <c r="X25" s="118">
+      <c r="P25" s="107"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="102"/>
+      <c r="T25" s="102"/>
+      <c r="U25" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V25" s="102"/>
+      <c r="W25" s="102"/>
+      <c r="X25" s="109">
         <v>20</v>
       </c>
-      <c r="Y25" s="119"/>
-    </row>
-    <row r="26" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y25" s="110"/>
+    </row>
+    <row r="26" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A26" s="11">
         <v>6</v>
       </c>
-      <c r="B26" s="111" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="109"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="111" t="s">
-        <v>104</v>
-      </c>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
-      <c r="X26" s="108" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y26" s="110"/>
-    </row>
-    <row r="27" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="B26" s="162" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="162" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="104"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="105"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="107"/>
+      <c r="Q26" s="102" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="V26" s="102"/>
+      <c r="W26" s="102"/>
+      <c r="X26" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y26" s="105"/>
+    </row>
+    <row r="27" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A27" s="26"/>
       <c r="X27" s="27"/>
       <c r="Y27" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="X25:Y25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="K26:N26"/>
@@ -4113,107 +5613,6 @@
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="K24:N24"/>
     <mergeCell ref="O24:P24"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="Q22:T22"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:Y7"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4224,7 +5623,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V24"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="4" customWidth="1"/>
     <col min="2" max="7" width="3.6640625" style="4"/>
@@ -4243,165 +5642,165 @@
     <col min="23" max="16384" width="3.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="86" t="s">
+    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="92" t="s">
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="66" t="s">
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="96" t="s">
+      <c r="R1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="97"/>
-      <c r="T1" s="71" t="s">
+      <c r="S1" s="77"/>
+      <c r="T1" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="67" t="s">
+      <c r="U1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="129"/>
-    </row>
-    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="130"/>
-    </row>
-    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="86" t="s">
+      <c r="V1" s="122"/>
+    </row>
+    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="123"/>
+    </row>
+    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="92" t="s">
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="66" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="96" t="s">
+      <c r="R3" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="97"/>
-      <c r="T3" s="66" t="s">
+      <c r="S3" s="77"/>
+      <c r="T3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="67" t="s">
+      <c r="U3" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="129"/>
-    </row>
-    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="130"/>
-    </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="102" t="s">
+      <c r="V3" s="122"/>
+    </row>
+    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="123"/>
+    </row>
+    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="102" t="s">
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="103" t="s">
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
       <c r="Q5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="103" t="s">
+      <c r="R5" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-    </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="S5" s="120"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="120"/>
+    </row>
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.8">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -4425,9 +5824,9 @@
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A7" s="8" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -4451,84 +5850,84 @@
       <c r="U7" s="9"/>
       <c r="V7" s="22"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="123" t="s">
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123" t="s">
+      <c r="J8" s="126"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="124" t="s">
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U8" s="75"/>
-      <c r="V8" s="76"/>
-    </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="U8" s="51"/>
+      <c r="V8" s="52"/>
+    </row>
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="11">
         <v>1</v>
       </c>
-      <c r="B9" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="117" t="s">
+      <c r="B9" s="124" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
-      <c r="S9" s="111"/>
-      <c r="T9" s="111" t="s">
-        <v>111</v>
-      </c>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
-    </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="102"/>
+      <c r="S9" s="102"/>
+      <c r="T9" s="102" t="s">
+        <v>90</v>
+      </c>
+      <c r="U9" s="102"/>
+      <c r="V9" s="102"/>
+    </row>
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="11">
         <v>2</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -4536,30 +5935,30 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="117" t="s">
+      <c r="I10" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="117" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="111"/>
-      <c r="S10" s="111"/>
-      <c r="T10" s="111" t="s">
-        <v>114</v>
-      </c>
-      <c r="U10" s="111"/>
-      <c r="V10" s="111"/>
-    </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="111" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="102" t="s">
+        <v>93</v>
+      </c>
+      <c r="U10" s="102"/>
+      <c r="V10" s="102"/>
+    </row>
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4583,9 +5982,9 @@
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
     </row>
-    <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="15" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -4609,153 +6008,153 @@
       <c r="U12" s="16"/>
       <c r="V12" s="23"/>
     </row>
-    <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="123" t="s">
+      <c r="B13" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123" t="s">
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123" t="s">
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="124" t="s">
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="124"/>
-      <c r="T13" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U13" s="75"/>
-      <c r="V13" s="76"/>
-    </row>
-    <row r="14" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="U13" s="51"/>
+      <c r="V13" s="52"/>
+    </row>
+    <row r="14" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="11">
         <v>1</v>
       </c>
-      <c r="B14" s="125" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J14" s="109"/>
-      <c r="K14" s="109"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="117" t="s">
+      <c r="B14" s="124" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-    </row>
-    <row r="15" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N14" s="102"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102" t="s">
+        <v>95</v>
+      </c>
+      <c r="U14" s="102"/>
+      <c r="V14" s="102"/>
+    </row>
+    <row r="15" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="11">
         <v>2</v>
       </c>
-      <c r="B15" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="117" t="s">
+      <c r="B15" s="124" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="117" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111" t="s">
-        <v>118</v>
-      </c>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-    </row>
-    <row r="16" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="111" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="102"/>
+      <c r="S15" s="102"/>
+      <c r="T15" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="U15" s="102"/>
+      <c r="V15" s="102"/>
+    </row>
+    <row r="16" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="11">
         <v>3</v>
       </c>
-      <c r="B16" s="127" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="117" t="s">
+      <c r="B16" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="105"/>
+      <c r="M16" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111" t="s">
-        <v>121</v>
-      </c>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-    </row>
-    <row r="18" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N16" s="102"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="U16" s="102"/>
+      <c r="V16" s="102"/>
+    </row>
+    <row r="18" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="15" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -4779,84 +6178,84 @@
       <c r="U18" s="16"/>
       <c r="V18" s="23"/>
     </row>
-    <row r="19" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="123" t="s">
+      <c r="B19" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123" t="s">
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123" t="s">
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="123"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="124" t="s">
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U19" s="75"/>
-      <c r="V19" s="76"/>
-    </row>
-    <row r="20" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q19" s="127"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="U19" s="51"/>
+      <c r="V19" s="52"/>
+    </row>
+    <row r="20" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="11">
         <v>1</v>
       </c>
-      <c r="B20" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="117" t="s">
+      <c r="B20" s="124" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111"/>
-      <c r="T20" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="U20" s="111"/>
-      <c r="V20" s="111"/>
-    </row>
-    <row r="21" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N20" s="102"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="102"/>
+      <c r="S20" s="102"/>
+      <c r="T20" s="102" t="s">
+        <v>95</v>
+      </c>
+      <c r="U20" s="102"/>
+      <c r="V20" s="102"/>
+    </row>
+    <row r="21" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="11">
         <v>2</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -4864,35 +6263,35 @@
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
-      <c r="I21" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="117" t="s">
+      <c r="I21" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="117" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111" t="s">
-        <v>123</v>
-      </c>
-      <c r="U21" s="111"/>
-      <c r="V21" s="111"/>
-    </row>
-    <row r="22" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N21" s="102"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="163" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="102"/>
+      <c r="S21" s="102"/>
+      <c r="T21" s="102" t="s">
+        <v>102</v>
+      </c>
+      <c r="U21" s="102"/>
+      <c r="V21" s="102"/>
+    </row>
+    <row r="22" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A22" s="11">
         <v>3</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -4900,35 +6299,35 @@
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
       <c r="H22" s="20"/>
-      <c r="I22" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="117" t="s">
+      <c r="I22" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="117" t="s">
-        <v>125</v>
-      </c>
-      <c r="U22" s="111"/>
-      <c r="V22" s="111"/>
-    </row>
-    <row r="23" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N22" s="102"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="162" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q22" s="102"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="102"/>
+      <c r="T22" s="111" t="s">
+        <v>104</v>
+      </c>
+      <c r="U22" s="102"/>
+      <c r="V22" s="102"/>
+    </row>
+    <row r="23" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="11">
         <v>4</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -4936,35 +6335,35 @@
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="20"/>
-      <c r="I23" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="117" t="s">
+      <c r="I23" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-    </row>
-    <row r="24" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N23" s="102"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="162" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q23" s="102"/>
+      <c r="R23" s="102"/>
+      <c r="S23" s="102"/>
+      <c r="T23" s="102" t="s">
+        <v>107</v>
+      </c>
+      <c r="U23" s="102"/>
+      <c r="V23" s="102"/>
+    </row>
+    <row r="24" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="11">
         <v>5</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -4972,85 +6371,46 @@
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="117" t="s">
+      <c r="I24" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111" t="s">
-        <v>131</v>
-      </c>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="162" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="102"/>
+      <c r="T24" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="U24" s="102"/>
+      <c r="V24" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="M1:P2"/>
-    <mergeCell ref="I3:L4"/>
-    <mergeCell ref="M3:P4"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="U3:V4"/>
-    <mergeCell ref="U1:V2"/>
-    <mergeCell ref="R3:S4"/>
-    <mergeCell ref="R1:S2"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="T21:V21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
     <mergeCell ref="I10:L10"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="P10:S10"/>
@@ -5060,24 +6420,1225 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:V13"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:V4"/>
+    <mergeCell ref="U1:V2"/>
+    <mergeCell ref="R3:S4"/>
+    <mergeCell ref="R1:S2"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="M1:P2"/>
+    <mergeCell ref="I3:L4"/>
+    <mergeCell ref="M3:P4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="27" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFDC482-01C3-434F-B7C2-D889C75281CF}">
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr defaultRowHeight="19.899999999999999" x14ac:dyDescent="0.8"/>
+  <cols>
+    <col min="11" max="11" width="15.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="130" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="135" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="67"/>
+      <c r="K1" s="133" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="46"/>
+      <c r="P1" s="158">
+        <v>45983</v>
+      </c>
+      <c r="Q1" s="159"/>
+    </row>
+    <row r="2" spans="1:17" s="130" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+    </row>
+    <row r="3" spans="1:17" s="130" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="67"/>
+      <c r="K3" s="133" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="46"/>
+      <c r="P3" s="160">
+        <v>45983</v>
+      </c>
+      <c r="Q3" s="159"/>
+    </row>
+    <row r="4" spans="1:17" s="130" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="159"/>
+      <c r="Q4" s="159"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="119" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="131" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="119" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="119"/>
+      <c r="K5" s="134" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="161" t="s">
+        <v>125</v>
+      </c>
+      <c r="M5" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+    </row>
+    <row r="6" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="153"/>
+    </row>
+    <row r="7" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="153"/>
+    </row>
+    <row r="8" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A8" s="153" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="153"/>
+    </row>
+    <row r="10" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A10" s="153"/>
+    </row>
+    <row r="11" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A11" s="153"/>
+    </row>
+    <row r="12" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A12" s="153"/>
+    </row>
+    <row r="13" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A13" s="153"/>
+    </row>
+    <row r="14" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A14" s="153"/>
+    </row>
+    <row r="15" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A15" s="153"/>
+    </row>
+    <row r="16" spans="1:17" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A16" s="153"/>
+    </row>
+    <row r="17" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A17" s="153"/>
+    </row>
+    <row r="18" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A18" s="153"/>
+    </row>
+    <row r="19" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A19" s="153"/>
+    </row>
+    <row r="20" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A20" s="153"/>
+    </row>
+    <row r="21" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A21" s="153"/>
+    </row>
+    <row r="22" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A22" s="153"/>
+    </row>
+    <row r="23" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A23" s="153"/>
+    </row>
+    <row r="24" spans="1:3" s="154" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A24" s="153"/>
+    </row>
+    <row r="25" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A25" s="155"/>
+      <c r="C25" s="157"/>
+    </row>
+    <row r="26" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A26" s="155"/>
+    </row>
+    <row r="27" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="155"/>
+    </row>
+    <row r="28" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A28" s="155"/>
+    </row>
+    <row r="29" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A29" s="155"/>
+    </row>
+    <row r="30" spans="1:3" s="156" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A30" s="155"/>
+    </row>
+    <row r="31" spans="1:3" s="141" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
+    <row r="32" spans="1:3" s="141" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
+    <row r="33" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="34" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="35" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="36" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="37" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="38" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+    <row r="39" s="141" customFormat="1" ht="15" x14ac:dyDescent="0.8"/>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="P1:Q2"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="P3:Q4"/>
+  </mergeCells>
+  <phoneticPr fontId="9"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38312257-DFBB-4A87-A9A2-1C6FD4FD3FE6}">
+  <dimension ref="A1:Q94"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.8"/>
+  <cols>
+    <col min="1" max="1" width="3.5" style="187" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="187" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" style="187" customWidth="1"/>
+    <col min="4" max="5" width="5.1640625" style="187" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" style="187" customWidth="1"/>
+    <col min="7" max="7" width="12.71875" style="187" customWidth="1"/>
+    <col min="8" max="8" width="3.71875" style="188" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="189" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" style="189" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="189" customWidth="1"/>
+    <col min="12" max="12" width="26.27734375" style="189" customWidth="1"/>
+    <col min="13" max="13" width="32" style="189" customWidth="1"/>
+    <col min="14" max="14" width="31" style="189" customWidth="1"/>
+    <col min="15" max="15" width="31" style="188" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="187"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="182" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="135" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="137" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="138"/>
+      <c r="K1" s="133" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="140" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="139" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="139"/>
+      <c r="P1" s="160">
+        <v>45983</v>
+      </c>
+      <c r="Q1" s="181"/>
+    </row>
+    <row r="2" spans="1:17" s="182" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="148"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="139"/>
+      <c r="P2" s="181"/>
+      <c r="Q2" s="181"/>
+    </row>
+    <row r="3" spans="1:17" s="182" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="137" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="138"/>
+      <c r="K3" s="133" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="140" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="139" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="139"/>
+      <c r="P3" s="160">
+        <v>45983</v>
+      </c>
+      <c r="Q3" s="181"/>
+    </row>
+    <row r="4" spans="1:17" s="182" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="149"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="181"/>
+      <c r="Q4" s="181"/>
+    </row>
+    <row r="5" spans="1:17" s="152" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="131" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="151" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="151"/>
+      <c r="K5" s="134" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="161" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="131" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="131"/>
+      <c r="O5" s="131"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="131"/>
+    </row>
+    <row r="6" spans="1:17" s="182" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="183" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="184" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="185"/>
+      <c r="O6" s="184" t="s">
+        <v>115</v>
+      </c>
+      <c r="P6" s="185"/>
+      <c r="Q6" s="185"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A7" s="186" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" s="190"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A8" s="187" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="189" t="s">
+        <v>161</v>
+      </c>
+      <c r="O8" s="188" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A9" s="187" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="189" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A11" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="164" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="165"/>
+      <c r="L11" s="166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A12" s="187" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="167" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="168"/>
+      <c r="L12" s="169" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A13" s="187" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="167" t="s">
+        <v>170</v>
+      </c>
+      <c r="K13" s="168"/>
+      <c r="L13" s="169" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A14" s="187" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14" s="167" t="s">
+        <v>172</v>
+      </c>
+      <c r="K14" s="168"/>
+      <c r="L14" s="169" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A15" s="187" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" s="167" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" s="168"/>
+      <c r="L15" s="169" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.8">
+      <c r="A16" s="187" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="167" t="s">
+        <v>176</v>
+      </c>
+      <c r="K16" s="168"/>
+      <c r="L16" s="169" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A17" s="187" t="s">
+        <v>141</v>
+      </c>
+      <c r="J17" s="167" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" s="168"/>
+      <c r="L17" s="169" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A19" s="187" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A20" s="187" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="164" t="s">
+        <v>188</v>
+      </c>
+      <c r="K20" s="165"/>
+      <c r="L20" s="166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A21" s="187" t="s">
+        <v>157</v>
+      </c>
+      <c r="J21" s="167" t="s">
+        <v>190</v>
+      </c>
+      <c r="K21" s="168"/>
+      <c r="L21" s="169" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A22" s="187" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22" s="167" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" s="168"/>
+      <c r="L22" s="169" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A23" s="187" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="167" t="s">
+        <v>194</v>
+      </c>
+      <c r="K23" s="168"/>
+      <c r="L23" s="169" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A24" s="187" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="167" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" s="168"/>
+      <c r="L24" s="169" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A25" s="187" t="s">
+        <v>156</v>
+      </c>
+      <c r="J25" s="167" t="s">
+        <v>198</v>
+      </c>
+      <c r="K25" s="168"/>
+      <c r="L25" s="169" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="J26" s="167" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="168"/>
+      <c r="L26" s="169" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="A27" s="187" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="I28" s="189" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="J29" s="172" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="J30" s="172" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="J31" s="173" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" s="173" t="s">
+        <v>206</v>
+      </c>
+      <c r="L31" s="173" t="s">
+        <v>207</v>
+      </c>
+      <c r="M31" s="173" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.8">
+      <c r="J32" s="191" t="s">
+        <v>208</v>
+      </c>
+      <c r="K32" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="L32" s="169" t="s">
+        <v>214</v>
+      </c>
+      <c r="M32" s="169" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J33" s="191"/>
+      <c r="K33" s="169" t="s">
+        <v>170</v>
+      </c>
+      <c r="L33" s="169" t="s">
+        <v>215</v>
+      </c>
+      <c r="M33" s="169" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J34" s="191"/>
+      <c r="K34" s="169" t="s">
+        <v>172</v>
+      </c>
+      <c r="L34" s="169" t="s">
+        <v>216</v>
+      </c>
+      <c r="M34" s="169" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J35" s="191"/>
+      <c r="K35" s="169" t="s">
+        <v>174</v>
+      </c>
+      <c r="L35" s="169" t="s">
+        <v>217</v>
+      </c>
+      <c r="M35" s="169" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J36" s="191"/>
+      <c r="K36" s="169" t="s">
+        <v>176</v>
+      </c>
+      <c r="L36" s="169" t="s">
+        <v>218</v>
+      </c>
+      <c r="M36" s="169" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J37" s="191"/>
+      <c r="K37" s="167" t="s">
+        <v>190</v>
+      </c>
+      <c r="L37" s="167" t="s">
+        <v>219</v>
+      </c>
+      <c r="M37" s="169" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J38" s="191"/>
+      <c r="K38" s="167" t="s">
+        <v>192</v>
+      </c>
+      <c r="L38" s="167" t="s">
+        <v>220</v>
+      </c>
+      <c r="M38" s="169" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J39" s="191"/>
+      <c r="K39" s="167" t="s">
+        <v>194</v>
+      </c>
+      <c r="L39" s="167" t="s">
+        <v>221</v>
+      </c>
+      <c r="M39" s="169" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="40" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J40" s="191"/>
+      <c r="K40" s="167" t="s">
+        <v>196</v>
+      </c>
+      <c r="L40" s="167" t="s">
+        <v>222</v>
+      </c>
+      <c r="M40" s="169" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J41" s="191"/>
+      <c r="K41" s="167" t="s">
+        <v>198</v>
+      </c>
+      <c r="L41" s="167" t="s">
+        <v>223</v>
+      </c>
+      <c r="M41" s="169" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J42" s="174" t="s">
+        <v>74</v>
+      </c>
+      <c r="K42" s="175"/>
+      <c r="L42" s="176" t="s">
+        <v>230</v>
+      </c>
+      <c r="M42" s="177" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="I44" s="189" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J45" s="189" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="47" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J47" s="189" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="9:13" x14ac:dyDescent="0.8">
+      <c r="J48" s="166" t="s">
+        <v>234</v>
+      </c>
+      <c r="K48" s="178" t="s">
+        <v>236</v>
+      </c>
+      <c r="L48" s="178"/>
+    </row>
+    <row r="49" spans="10:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="J49" s="169" t="s">
+        <v>235</v>
+      </c>
+      <c r="K49" s="180" t="s">
+        <v>240</v>
+      </c>
+      <c r="L49" s="179"/>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J51" s="192" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J52" s="166" t="s">
+        <v>241</v>
+      </c>
+      <c r="K52" s="178" t="s">
+        <v>242</v>
+      </c>
+      <c r="L52" s="178"/>
+    </row>
+    <row r="53" spans="10:12" ht="33" x14ac:dyDescent="0.8">
+      <c r="J53" s="177" t="s">
+        <v>261</v>
+      </c>
+      <c r="K53" s="193" t="s">
+        <v>243</v>
+      </c>
+      <c r="L53" s="193"/>
+    </row>
+    <row r="54" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J54" s="194" t="s">
+        <v>245</v>
+      </c>
+      <c r="K54" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="L54" s="193"/>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J55" s="193" t="s">
+        <v>257</v>
+      </c>
+      <c r="K55" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="L55" s="193"/>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J56" s="194" t="s">
+        <v>258</v>
+      </c>
+      <c r="K56" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="L56" s="193"/>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J57" s="193" t="s">
+        <v>259</v>
+      </c>
+      <c r="K57" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="L57" s="193"/>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J58" s="193" t="s">
+        <v>260</v>
+      </c>
+      <c r="K58" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="L58" s="193"/>
+    </row>
+    <row r="59" spans="10:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="J59" s="193" t="s">
+        <v>262</v>
+      </c>
+      <c r="K59" s="196" t="s">
+        <v>263</v>
+      </c>
+      <c r="L59" s="197"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J61" s="192" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J62" s="166" t="s">
+        <v>246</v>
+      </c>
+      <c r="K62" s="178" t="s">
+        <v>242</v>
+      </c>
+      <c r="L62" s="178"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J63" s="169" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63" s="193" t="s">
+        <v>247</v>
+      </c>
+      <c r="L63" s="193"/>
+    </row>
+    <row r="64" spans="10:12" x14ac:dyDescent="0.8">
+      <c r="J64" s="169" t="s">
+        <v>65</v>
+      </c>
+      <c r="K64" s="193" t="s">
+        <v>249</v>
+      </c>
+      <c r="L64" s="193"/>
+    </row>
+    <row r="65" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J65" s="169" t="s">
+        <v>67</v>
+      </c>
+      <c r="K65" s="193" t="s">
+        <v>252</v>
+      </c>
+      <c r="L65" s="193"/>
+    </row>
+    <row r="66" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J66" s="169" t="s">
+        <v>69</v>
+      </c>
+      <c r="K66" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="L66" s="193"/>
+    </row>
+    <row r="67" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J67" s="169" t="s">
+        <v>71</v>
+      </c>
+      <c r="K67" s="193" t="s">
+        <v>250</v>
+      </c>
+      <c r="L67" s="193"/>
+    </row>
+    <row r="68" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J68" s="167" t="s">
+        <v>76</v>
+      </c>
+      <c r="K68" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="L68" s="193"/>
+    </row>
+    <row r="69" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J69" s="167" t="s">
+        <v>82</v>
+      </c>
+      <c r="K69" s="193" t="s">
+        <v>254</v>
+      </c>
+      <c r="L69" s="193"/>
+    </row>
+    <row r="72" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J72" s="192" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="73" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J73" s="192" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J74" s="192" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="76" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J76" s="172"/>
+    </row>
+    <row r="77" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="I77" s="189" t="s">
+        <v>265</v>
+      </c>
+      <c r="J77" s="172"/>
+      <c r="O77" s="201" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="78" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J78" s="189" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="79" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J79" s="198" t="s">
+        <v>267</v>
+      </c>
+      <c r="K79" s="166" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="9:15" x14ac:dyDescent="0.8">
+      <c r="J80" s="167" t="s">
+        <v>88</v>
+      </c>
+      <c r="K80" s="169" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J81" s="167" t="s">
+        <v>91</v>
+      </c>
+      <c r="K81" s="169" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="83" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J83" s="189" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J84" s="198" t="s">
+        <v>267</v>
+      </c>
+      <c r="K84" s="166" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J85" s="167" t="s">
+        <v>88</v>
+      </c>
+      <c r="K85" s="169" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="86" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J86" s="167" t="s">
+        <v>91</v>
+      </c>
+      <c r="K86" s="169" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="88" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J88" s="189" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="89" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J89" s="198" t="s">
+        <v>267</v>
+      </c>
+      <c r="K89" s="166" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J90" s="167" t="s">
+        <v>88</v>
+      </c>
+      <c r="K90" s="169" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="91" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J91" s="167" t="s">
+        <v>91</v>
+      </c>
+      <c r="K91" s="169" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="92" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J92" s="167" t="s">
+        <v>273</v>
+      </c>
+      <c r="K92" s="169" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J93" s="167" t="s">
+        <v>274</v>
+      </c>
+      <c r="K93" s="169" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="10:11" x14ac:dyDescent="0.8">
+      <c r="J94" s="167" t="s">
+        <v>275</v>
+      </c>
+      <c r="K94" s="169" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J32:J41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="P1:Q2"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="P3:Q4"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:O2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="A7" r:id="rId1" display="URL:POST /api/parts/stock/receive" xr:uid="{F7BD535B-88B3-4889-A388-C20BB62FB993}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>